--- a/output_pdfs/n_r_5_n_converted.xlsx
+++ b/output_pdfs/n_r_5_n_converted.xlsx
@@ -571,7 +571,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>1/9/22</t>
+          <t>01/09/2022</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>2/9/22</t>
+          <t>02/09/2022</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>4/9/22</t>
+          <t>04/09/2022</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -646,7 +646,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>5/9/22</t>
+          <t>05/09/2022</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>6/9/22</t>
+          <t>06/09/2022</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -696,7 +696,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>7/9/22</t>
+          <t>07/09/2022</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>8/9/22</t>
+          <t>08/09/2022</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -746,12 +746,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>9/9/122</t>
+          <t>09/09/2022</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>רביעי</t>
+          <t>שישי</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>11/9/22</t>
+          <t>11/09/2022</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>12/9/22</t>
+          <t>12/09/2022</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -821,7 +821,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>13/9/22</t>
+          <t>13/09/2022</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -846,7 +846,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>14/9/22</t>
+          <t>14/09/2022</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>15/9/22</t>
+          <t>15/09/2022</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -896,7 +896,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>16/9/22</t>
+          <t>16/09/2022</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -921,7 +921,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>18/9/22</t>
+          <t>18/09/2022</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>19/9/22</t>
+          <t>19/09/2022</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>20/9/22</t>
+          <t>20/09/2022</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -996,7 +996,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>21/9/22</t>
+          <t>21/09/2022</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>22/9/22</t>
+          <t>22/09/2022</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1046,7 +1046,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>23/9/22</t>
+          <t>23/09/2022</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -1071,7 +1071,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>28/9/22</t>
+          <t>28/09/2022</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -1096,7 +1096,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>29/9/22</t>
+          <t>29/09/2022</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -1121,7 +1121,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>30/9/22</t>
+          <t>30/09/2022</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">

--- a/output_pdfs/n_r_5_n_converted.xlsx
+++ b/output_pdfs/n_r_5_n_converted.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דוח נוכחות חודשי" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="דוח נוכחות חודשי" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
